--- a/Validate_Paired_TTest.xlsx
+++ b/Validate_Paired_TTest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost_TTest" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FillRate_TTest" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cost_TTest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FillRate_TTest" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -660,28 +660,28 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>294123.57576</v>
+        <v>83128.25876</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>11767.11598</v>
+        <v>55269.7481</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>282356.45978</v>
+        <v>27858.51066</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>11593.78821266008</v>
+        <v>2747.261921787242</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>54.45745828484512</v>
+        <v>22.67476686283238</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>6.806849087139168e-07</v>
+        <v>2.240626827934166e-05</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>0.9999996596575457</v>
+        <v>0.9999887968658603</v>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
@@ -702,28 +702,28 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>294123.57576</v>
+        <v>83128.25876</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>264227.33266</v>
+        <v>65732.06165999999</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>29896.2431</v>
+        <v>17396.1971</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>15414.88125260206</v>
+        <v>2726.309143147087</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4.336720520125619</v>
+        <v>14.26803683043881</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.01228457520794053</v>
+        <v>0.0001401536585802731</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.9938577123960297</v>
+        <v>0.9999299231707098</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
@@ -744,28 +744,28 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>294123.57576</v>
+        <v>83128.25876</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>262185.04354</v>
+        <v>65769.2102</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>31938.53222000002</v>
+        <v>17359.04856</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>15341.70268434127</v>
+        <v>2724.254378437858</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>4.655071905309429</v>
+        <v>14.24830695404359</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.009624910152724691</v>
+        <v>0.0001409190121216709</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0.9951875449236377</v>
+        <v>0.9999295404939391</v>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
@@ -790,28 +790,28 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>116941.21104</v>
+        <v>74449.27092000001</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>71590.54244</v>
+        <v>73949.04883999999</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>45350.6686</v>
+        <v>500.2220799999981</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>5756.576742754474</v>
+        <v>510.7469930196734</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>17.61588220678227</v>
+        <v>2.189989544751464</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>6.099029710906764e-05</v>
+        <v>0.09369317114097075</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.9999695048514454</v>
+        <v>0.9531534144295146</v>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
@@ -832,28 +832,28 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>116941.21104</v>
+        <v>74449.27092000001</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>105435.04684</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>11506.1642</v>
+        <v>2899.445379999999</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>9013.387411970418</v>
+        <v>273.9738515819229</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>2.854483462821661</v>
+        <v>23.66414506089852</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.04618605273746831</v>
+        <v>1.890755359886417e-05</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0.9769069736312659</v>
+        <v>0.9999905462232006</v>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>116941.21104</v>
+        <v>74449.27092000001</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>109947.82728</v>
+        <v>71549.82554000001</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>6993.38376</v>
+        <v>2899.445379999999</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>5744.671084704778</v>
+        <v>273.9738515819229</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2.722119552107778</v>
+        <v>23.66414506089852</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.05287104065118883</v>
+        <v>1.890755359886417e-05</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0.9735644796744056</v>
+        <v>0.9999905462232006</v>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
@@ -920,28 +920,28 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>417673.33198</v>
+        <v>90363.50659999999</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>174952.73972</v>
+        <v>87473.67942</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>242720.59226</v>
+        <v>2889.827179999999</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>45265.08714250112</v>
+        <v>912.2747288246039</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>11.99025072289699</v>
+        <v>7.083228125843315</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.000277308356946125</v>
+        <v>0.002097080065468473</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0.999861345821527</v>
+        <v>0.9989514599672658</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
@@ -962,37 +962,37 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>417673.33198</v>
+        <v>90363.50659999999</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>364807.10478</v>
+        <v>102410.96022</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>52866.22720000001</v>
+        <v>-12047.45362</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>17948.35178885999</v>
+        <v>3168.473051751469</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>6.586258121289966</v>
+        <v>-8.502179065466445</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.002751910368640813</v>
+        <v>0.001049548590091933</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0.9986240448156796</v>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>n.s.</t>
-        </is>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>No significant difference</t>
+        <v>0.0005247742950459667</v>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>GNN significantly lower cost</t>
         </is>
       </c>
     </row>
@@ -1004,37 +1004,37 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>417673.33198</v>
+        <v>90363.50659999999</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>367803.24106</v>
+        <v>101424.45222</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>49870.09092000001</v>
+        <v>-11060.94562</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>23373.8629793765</v>
+        <v>4394.543990546775</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4.770837984273564</v>
+        <v>-5.628121223715694</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.008834645389960009</v>
+        <v>0.004902370417424772</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0.99558267730502</v>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>n.s.</t>
-        </is>
-      </c>
-      <c r="L12" s="10" t="inlineStr">
-        <is>
-          <t>No significant difference</t>
+        <v>0.002451185208712386</v>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>GNN significantly lower cost</t>
         </is>
       </c>
     </row>
@@ -1053,25 +1053,25 @@
         <v>212106.58592</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>170826.34104</v>
+        <v>238068.45244</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>41280.24488</v>
+        <v>-25961.86652</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>12502.97840760829</v>
+        <v>36547.04043839888</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>7.382675604986098</v>
+        <v>-1.588432268800127</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.001794560786938412</v>
+        <v>0.1873858217623071</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0.9991027196065307</v>
+        <v>0.09369291088115353</v>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
@@ -1095,34 +1095,34 @@
         <v>212106.58592</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>209895.49308</v>
+        <v>251676.6231</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2211.092839999998</v>
+        <v>-39570.03718</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>7752.702986473484</v>
+        <v>17731.86507478504</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.6377329175939495</v>
+        <v>-4.989959749496161</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.5583250869961386</v>
+        <v>0.007543870941548818</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0.7208374565019307</v>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>n.s.</t>
-        </is>
-      </c>
-      <c r="L14" s="10" t="inlineStr">
-        <is>
-          <t>No significant difference</t>
+        <v>0.003771935470774409</v>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>GNN significantly lower cost</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
         <v>0.004790006370363769</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0.002395003185181884</v>
+        <v>0.002395003185181885</v>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
@@ -1198,10 +1198,10 @@
         <v>4</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.06543800121481592</v>
+        <v>0.0654380012148159</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.03271900060740796</v>
+        <v>0.03271900060740795</v>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         <v>4</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.004084776045440385</v>
+        <v>0.004084776045440386</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0.002042388022720192</v>
+        <v>0.002042388022720193</v>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
@@ -1282,10 +1282,10 @@
         <v>4</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.006001728190183478</v>
+        <v>0.006001728190183481</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>0.003000864095091739</v>
+        <v>0.003000864095091741</v>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         <v>4</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>4.975637728306554e-05</v>
+        <v>4.975637728306548e-05</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>2.487818864153277e-05</v>
+        <v>2.487818864153274e-05</v>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
@@ -1458,10 +1458,10 @@
         <v>4</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>3.004158243388331e-05</v>
+        <v>3.004158243388328e-05</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>1.502079121694165e-05</v>
+        <v>1.502079121694164e-05</v>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
@@ -1542,10 +1542,10 @@
         <v>4</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0002051439630539623</v>
+        <v>0.0002051439630539624</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>0.0001025719815269811</v>
+        <v>0.0001025719815269812</v>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -1573,25 +1573,25 @@
         <v>73621.48692</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>56282.888</v>
+        <v>88719.47573999999</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>17338.59892</v>
+        <v>-15097.98882</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>9402.45937944855</v>
+        <v>19573.60692451679</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>4.123419655974978</v>
+        <v>-1.724778139013603</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.01457177362260935</v>
+        <v>0.1596548534198025</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>0.9927141131886953</v>
+        <v>0.07982742670990123</v>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
         <v>4</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>4.566932261858725e-05</v>
+        <v>4.566932261858727e-05</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>2.283466130929362e-05</v>
+        <v>2.283466130929364e-05</v>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         <v>4</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>4.566932261858725e-05</v>
+        <v>4.566932261858727e-05</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>2.283466130929362e-05</v>
+        <v>2.283466130929364e-05</v>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
@@ -1700,37 +1700,37 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>388358.1053</v>
+        <v>128190.88714</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>332468.28218</v>
+        <v>142650.96726</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>55889.82311999999</v>
+        <v>-14460.08012</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>22704.27975760717</v>
+        <v>14742.3006166183</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>5.504400275233856</v>
+        <v>-2.193261618336899</v>
       </c>
       <c r="H28" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.005312772611076064</v>
+        <v>0.09335163993339664</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>0.997343613694462</v>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>n.s.</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="inlineStr">
-        <is>
-          <t>No significant difference</t>
+        <v>0.04667581996669832</v>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="L28" s="14" t="inlineStr">
+        <is>
+          <t>GNN significantly lower cost</t>
         </is>
       </c>
     </row>
@@ -1742,37 +1742,37 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>388358.1053</v>
+        <v>128190.88714</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>431016.02148</v>
+        <v>131516.09112</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-42657.91618000001</v>
+        <v>-3325.203979999997</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>15386.88908090938</v>
+        <v>5375.967635227243</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-6.199173845694011</v>
+        <v>-1.383077920635315</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.003443467560247164</v>
+        <v>0.2388306825703071</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0.001721733780123582</v>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
-      <c r="L29" s="14" t="inlineStr">
-        <is>
-          <t>GNN significantly lower cost</t>
+        <v>0.1194153412851536</v>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>No significant difference</t>
         </is>
       </c>
     </row>
@@ -1784,37 +1784,37 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>388358.1053</v>
+        <v>128190.88714</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>411428.11356</v>
+        <v>131516.09112</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-23070.00826000001</v>
+        <v>-3325.203979999997</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>22017.53019469357</v>
+        <v>5375.967635227243</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-2.342956101555587</v>
+        <v>-1.383077920635315</v>
       </c>
       <c r="H30" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.07912213248084406</v>
+        <v>0.2388306825703071</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>0.03956106624042203</v>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="L30" s="14" t="inlineStr">
-        <is>
-          <t>GNN significantly lower cost</t>
+        <v>0.1194153412851536</v>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>No significant difference</t>
         </is>
       </c>
     </row>
@@ -1833,25 +1833,25 @@
         <v>710559.3757999999</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>676888.7525199999</v>
+        <v>742692.97098</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>33670.62327999999</v>
+        <v>-32133.59518000004</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>76410.66105307285</v>
+        <v>49811.00403549529</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.9853311234485013</v>
+        <v>-1.442510637463508</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.3802449616308326</v>
+        <v>0.2226254271348335</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>0.8098775191845837</v>
+        <v>0.1113127135674168</v>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         <v>4</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.5988563363385188</v>
+        <v>0.5988563363385186</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>0.2994281681692594</v>
+        <v>0.2994281681692593</v>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
@@ -1932,10 +1932,10 @@
         <v>4</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.168058763302101</v>
+        <v>0.1680587633021011</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>0.08402938165105051</v>
+        <v>0.08402938165105053</v>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
@@ -2069,37 +2069,37 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>60.24364000000001</v>
+        <v>98.58438000000001</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>95.52536000000001</v>
+        <v>97.74202</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-35.28171999999999</v>
+        <v>0.8423599999999937</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>2.58652864704801</v>
+        <v>0.5606020718834365</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-30.50123739134041</v>
+        <v>3.359913057756861</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>6.882966844189611e-06</v>
+        <v>0.0283071270133191</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>0.9999965585165779</v>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>n.s.</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>No significant difference</t>
+        <v>0.01415356350665955</v>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>GNN significantly higher fill rate</t>
         </is>
       </c>
     </row>
@@ -2111,28 +2111,28 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>60.24364000000001</v>
+        <v>98.58438000000001</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>76.65346</v>
+        <v>100</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-16.40982</v>
+        <v>-1.415620000000004</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2.823996800989691</v>
+        <v>0.3075080925764394</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-12.99345417306284</v>
+        <v>-10.29378616929052</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0002024395205267557</v>
+        <v>0.0005023531672333353</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.9998987802397367</v>
+        <v>0.9997488234163834</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
@@ -2153,28 +2153,28 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>60.24364000000001</v>
+        <v>98.58438000000001</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>77.84826000000001</v>
+        <v>100</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-17.60462</v>
+        <v>-1.415620000000004</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2.480654817180336</v>
+        <v>0.3075080925764394</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-15.86884509905218</v>
+        <v>-10.29378616929052</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>9.216353096297626e-05</v>
+        <v>0.0005023531672333353</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0.9999539182345185</v>
+        <v>0.9997488234163834</v>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
@@ -2199,32 +2199,32 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>91.67654</v>
+        <v>99.89196</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>4.605260000000001</v>
+        <v>0.1080399999999997</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1.458779924457422</v>
+        <v>0.08852543702236282</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>7.059100719315695</v>
+        <v>2.728987197522096</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.002124101932942551</v>
+        <v>0.05249776132682606</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.001062050966471276</v>
+        <v>0.02624888066341303</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>*</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
@@ -2241,37 +2241,37 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>78.01594</v>
+        <v>100</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>18.26586</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1.600929220171836</v>
+        <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>25.5124986869253</v>
+        <v/>
       </c>
       <c r="H8" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>1.40185820195998e-05</v>
+        <v/>
       </c>
       <c r="J8" s="8" t="n">
-        <v>7.009291009799901e-06</v>
-      </c>
-      <c r="K8" s="13" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>GNN significantly higher fill rate</t>
+        <v/>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>No significant difference</t>
         </is>
       </c>
     </row>
@@ -2283,37 +2283,37 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>96.2818</v>
+        <v>100</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>78.28578</v>
+        <v>100</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>17.99602</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1.132362211043795</v>
+        <v>0</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>35.53661862961042</v>
+        <v/>
       </c>
       <c r="H9" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>3.742464162381745e-06</v>
+        <v/>
       </c>
       <c r="J9" s="8" t="n">
-        <v>1.871232081190873e-06</v>
-      </c>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-      <c r="L9" s="14" t="inlineStr">
-        <is>
-          <t>GNN significantly higher fill rate</t>
+        <v/>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>n.s.</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>No significant difference</t>
         </is>
       </c>
     </row>
@@ -2329,37 +2329,37 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>86.72666</v>
+        <v>98.01527999999999</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-7.51064</v>
+        <v>1.984720000000002</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>5.089825370088838</v>
+        <v>0.3791459244143317</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-3.299583064916802</v>
+        <v>11.7051735243066</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.02994511893673354</v>
+        <v>0.0003046478197303142</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0.9850274405316333</v>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>n.s.</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>No significant difference</t>
+        <v>0.0001523239098651571</v>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>GNN significantly higher fill rate</t>
         </is>
       </c>
     </row>
@@ -2371,28 +2371,28 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>79.23348000000001</v>
+        <v>100</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-0.01746000000000265</v>
+        <v>0</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>2.35166027903692</v>
+        <v>0</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.01660178012750255</v>
+        <v/>
       </c>
       <c r="H11" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.9875493798163608</v>
+        <v/>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0.5062253100918196</v>
+        <v/>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
@@ -2413,28 +2413,28 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>79.21602</v>
+        <v>100</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>79.29212000000001</v>
+        <v>100</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.07610000000000242</v>
+        <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3.431713832037862</v>
+        <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.04958594492906482</v>
+        <v/>
       </c>
       <c r="H12" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.9628295790521887</v>
+        <v/>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0.5185852104739057</v>
+        <v/>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
@@ -2462,29 +2462,29 @@
         <v>93.32698000000001</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>90.72194</v>
+        <v>90.55726000000001</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2.605039999999994</v>
+        <v>2.769719999999998</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1.120950994914585</v>
+        <v>2.042231656056678</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>5.196522016156377</v>
+        <v>3.032605130898447</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.006531718798929602</v>
+        <v>0.03868157397864042</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0.003265859399464801</v>
+        <v>0.01934078698932021</v>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>*</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
@@ -2504,25 +2504,25 @@
         <v>93.32698000000001</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>78.11203999999999</v>
+        <v>76.19785999999999</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>15.21494</v>
+        <v>17.12912</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.5181780224980603</v>
+        <v>1.781025170232021</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>65.65627764289829</v>
+        <v>21.50552241199458</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>3.22385035836837e-07</v>
+        <v>2.765137876797169e-05</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>1.611925179184185e-07</v>
+        <v>1.382568938398584e-05</v>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -2561,10 +2561,10 @@
         <v>4</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>5.118257599457561e-06</v>
+        <v>5.118257599457554e-06</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>2.559128799728781e-06</v>
+        <v>2.559128799728777e-06</v>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
         <v>4</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.007189297129454753</v>
+        <v>0.00718929712945476</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.003594648564727377</v>
+        <v>0.00359464856472738</v>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
@@ -2649,10 +2649,10 @@
         <v>4</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>3.968083399249811e-05</v>
+        <v>3.96808339924981e-05</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>1.984041699624906e-05</v>
+        <v>1.984041699624905e-05</v>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
@@ -2691,10 +2691,10 @@
         <v>4</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>6.338270443166205e-05</v>
+        <v>6.338270443166213e-05</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>3.169135221583102e-05</v>
+        <v>3.169135221583106e-05</v>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
@@ -2779,10 +2779,10 @@
         <v>4</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>7.715957883493165e-06</v>
+        <v>7.715957883493178e-06</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>3.857978941746582e-06</v>
+        <v>3.857978941746589e-06</v>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         <v>4</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>2.113248485702416e-05</v>
+        <v>2.113248485702419e-05</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>1.056624242851208e-05</v>
+        <v>1.056624242851209e-05</v>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
@@ -2867,10 +2867,10 @@
         <v>4</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>1.952825544805747e-05</v>
+        <v>1.952825544805749e-05</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>9.764127724028733e-06</v>
+        <v>9.764127724028743e-06</v>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
         <v>4</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>5.912279632131416e-07</v>
+        <v>5.912279632131408e-07</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>2.956139816065708e-07</v>
+        <v>2.956139816065704e-07</v>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         <v>4</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>1.583304941653489e-06</v>
+        <v>1.583304941653487e-06</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>7.916524708267447e-07</v>
+        <v>7.916524708267435e-07</v>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -2982,25 +2982,25 @@
         <v>93.75758</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>95.48144000000001</v>
+        <v>95.30121999999999</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>-1.723859999999999</v>
+        <v>-1.543639999999996</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.4040114639462665</v>
+        <v>0.7220505266253917</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-9.540987045371208</v>
+        <v>-4.780391185253634</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0006739431354865003</v>
+        <v>0.008773019725606851</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>0.9996630284322567</v>
+        <v>0.9956134901371966</v>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
@@ -3039,10 +3039,10 @@
         <v>4</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>1.257235191951037e-05</v>
+        <v>1.257235191951036e-05</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>6.286175959755185e-06</v>
+        <v>6.286175959755182e-06</v>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
@@ -3081,10 +3081,10 @@
         <v>4</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>1.257235191951037e-05</v>
+        <v>1.257235191951036e-05</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>6.286175959755185e-06</v>
+        <v>6.286175959755182e-06</v>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
@@ -3109,37 +3109,37 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>84.27312000000001</v>
+        <v>99.76740000000001</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>90.82626</v>
+        <v>95.89005999999999</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-6.553140000000002</v>
+        <v>3.877340000000004</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1.170393296289756</v>
+        <v>0.2557355821937959</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-12.51995081698182</v>
+        <v>33.90218810188463</v>
       </c>
       <c r="H28" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0002341488475377477</v>
+        <v>4.515704037820993e-06</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>0.9998829255762312</v>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>n.s.</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="inlineStr">
-        <is>
-          <t>No significant difference</t>
+        <v>2.257852018910497e-06</v>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="L28" s="14" t="inlineStr">
+        <is>
+          <t>GNN significantly higher fill rate</t>
         </is>
       </c>
     </row>
@@ -3151,28 +3151,28 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>84.27312000000001</v>
+        <v>99.76740000000001</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>77.58844000000001</v>
+        <v>97.98776000000001</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>6.68468</v>
+        <v>1.779640000000001</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.8383873192027694</v>
+        <v>0.505181653467344</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>17.82875115769513</v>
+        <v>7.877158618419548</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>5.81585326879881e-05</v>
+        <v>0.001404090880836876</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>2.907926634399405e-05</v>
+        <v>0.0007020454404184378</v>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
@@ -3193,28 +3193,28 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>84.27312000000001</v>
+        <v>99.76740000000001</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>77.66758000000002</v>
+        <v>97.98776000000001</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>6.60554</v>
+        <v>1.779640000000001</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.7526950863397492</v>
+        <v>0.505181653467344</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>19.62339961579997</v>
+        <v>7.877158618419548</v>
       </c>
       <c r="H30" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>3.977156659954861e-05</v>
+        <v>0.001404090880836876</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>1.98857832997743e-05</v>
+        <v>0.0007020454404184378</v>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
         <v>94.87696</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>87.71088</v>
+        <v>87.47286000000001</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>7.166079999999996</v>
+        <v>7.404099999999997</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1.145177980490367</v>
+        <v>1.38915436687216</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>13.99244683812402</v>
+        <v>11.91809298305995</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0001513322797640375</v>
+        <v>0.0002839296355367743</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>7.566613988201875e-05</v>
+        <v>0.0001419648177683871</v>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
@@ -3299,10 +3299,10 @@
         <v>4</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>4.737199898957385e-07</v>
+        <v>4.737199898957377e-07</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>2.368599949478693e-07</v>
+        <v>2.368599949478688e-07</v>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
         <v>4</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>5.710631465581366e-07</v>
+        <v>5.710631465581363e-07</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>2.855315732790683e-07</v>
+        <v>2.855315732790682e-07</v>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
@@ -3433,17 +3433,17 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>n.s. (+2399.5%)</t>
+          <t>n.s. (+50.4%)</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>n.s. (+11.3%)</t>
+          <t>n.s. (+26.5%)</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>n.s. (+12.2%)</t>
+          <t>n.s. (+26.4%)</t>
         </is>
       </c>
     </row>
@@ -3455,17 +3455,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>n.s. (+63.3%)</t>
+          <t>n.s. (+0.7%)</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>n.s. (+10.9%)</t>
+          <t>n.s. (+4.1%)</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>n.s. (+6.4%)</t>
+          <t>n.s. (+4.1%)</t>
         </is>
       </c>
     </row>
@@ -3477,17 +3477,17 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>n.s. (+138.7%)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>n.s. (+14.5%)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>n.s. (+13.6%)</t>
+          <t>n.s. (+3.3%)</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>GNN wins (-11.8%) ***</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>GNN wins (-10.9%) **</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>n.s. (+24.2%)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>n.s. (+1.1%)</t>
+          <t>n.s. (-10.9%)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>GNN wins (-15.7%) **</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>n.s. (+30.8%)</t>
+          <t>n.s. (-17.0%)</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -3607,19 +3607,19 @@
           <t>4x30</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>n.s. (+16.8%)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>GNN wins (-9.9%) **</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>GNN wins (-5.6%) *</t>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>GNN wins (-10.1%) *</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>n.s. (-2.5%)</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>n.s. (-2.5%)</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>n.s. (+5.0%)</t>
+          <t>n.s. (-4.3%)</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -3702,19 +3702,19 @@
           <t>1x3</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>n.s. (-35.28pp)</t>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>GNN wins (+0.84pp) *</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>n.s. (-16.41pp)</t>
+          <t>n.s. (-1.42pp)</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>n.s. (-17.60pp)</t>
+          <t>n.s. (-1.42pp)</t>
         </is>
       </c>
     </row>
@@ -3726,17 +3726,17 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>GNN wins (+4.61pp) **</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>GNN wins (+18.27pp) ***</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>GNN wins (+18.00pp) ***</t>
+          <t>GNN wins (+0.11pp) *</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>n.s. (+0.00pp)</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>n.s. (+0.00pp)</t>
         </is>
       </c>
     </row>
@@ -3746,19 +3746,19 @@
           <t>1x10</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>n.s. (-7.51pp)</t>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>GNN wins (+1.98pp) ***</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>n.s. (-0.02pp)</t>
+          <t>n.s. (+0.00pp)</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>n.s. (-0.08pp)</t>
+          <t>n.s. (+0.00pp)</t>
         </is>
       </c>
     </row>
@@ -3770,12 +3770,12 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>GNN wins (+2.61pp) **</t>
+          <t>GNN wins (+2.77pp) *</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>GNN wins (+15.21pp) ***</t>
+          <t>GNN wins (+17.13pp) ***</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>n.s. (-1.72pp)</t>
+          <t>n.s. (-1.54pp)</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
@@ -3878,19 +3878,19 @@
           <t>4x30</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>n.s. (-6.55pp)</t>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>GNN wins (+3.88pp) ***</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>GNN wins (+6.68pp) ***</t>
+          <t>GNN wins (+1.78pp) ***</t>
         </is>
       </c>
       <c r="D29" s="18" t="inlineStr">
         <is>
-          <t>GNN wins (+6.61pp) ***</t>
+          <t>GNN wins (+1.78pp) ***</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>GNN wins (+7.17pp) ***</t>
+          <t>GNN wins (+7.40pp) ***</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
@@ -3924,17 +3924,17 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>

--- a/Validate_Paired_TTest.xlsx
+++ b/Validate_Paired_TTest.xlsx
@@ -1053,34 +1053,34 @@
         <v>212106.58592</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>238068.45244</v>
+        <v>243090.99876</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-25961.86652</v>
+        <v>-30984.41284</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>36547.04043839888</v>
+        <v>22684.98662907585</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-1.588432268800127</v>
+        <v>-3.05414565527473</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.1873858217623071</v>
+        <v>0.03787443873473434</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0.09369291088115353</v>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>n.s.</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>No significant difference</t>
+        <v>0.01893721936736717</v>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>GNN significantly lower cost</t>
         </is>
       </c>
     </row>
@@ -1095,29 +1095,29 @@
         <v>212106.58592</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>251676.6231</v>
+        <v>226841.5428</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-39570.03718</v>
+        <v>-14734.95687999999</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>17731.86507478504</v>
+        <v>12710.73593127587</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-4.989959749496161</v>
+        <v>-2.592168180296775</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.007543870941548818</v>
+        <v>0.06054541084871985</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0.003771935470774409</v>
+        <v>0.03027270542435993</v>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>*</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
@@ -2462,29 +2462,29 @@
         <v>93.32698000000001</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>90.55726000000001</v>
+        <v>90.27560000000001</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2.769719999999998</v>
+        <v>3.05138</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>2.042231656056678</v>
+        <v>1.357547793633802</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3.032605130898447</v>
+        <v>5.026042646292153</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.03868157397864042</v>
+        <v>0.007353962530607591</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0.01934078698932021</v>
+        <v>0.003676981265303796</v>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
@@ -2504,25 +2504,25 @@
         <v>93.32698000000001</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>76.19785999999999</v>
+        <v>77.29986</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>17.12912</v>
+        <v>16.02712</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1.781025170232021</v>
+        <v>0.7807528270842171</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>21.50552241199458</v>
+        <v>45.90150500944742</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>4</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>2.765137876797169e-05</v>
+        <v>1.347319612021357e-06</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>1.382568938398584e-05</v>
+        <v>6.736598060106783e-07</v>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -3497,14 +3497,14 @@
           <t>2x15</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>n.s. (-10.9%)</t>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>GNN wins (-12.7%) *</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>GNN wins (-15.7%) **</t>
+          <t>GNN wins (-6.5%) *</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>GNN wins (+2.77pp) *</t>
+          <t>GNN wins (+3.05pp) **</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>GNN wins (+17.13pp) ***</t>
+          <t>GNN wins (+16.03pp) ***</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
